--- a/artfynd/A 60399-2024 artfynd.xlsx
+++ b/artfynd/A 60399-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -873,6 +873,218 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>134635859</v>
+      </c>
+      <c r="B4" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Vasikkajoki, Nb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>855231</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7477868</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Färskt ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>134635860</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Vasikkajoki, Nb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>855220</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7477866</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färskt ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 60399-2024 artfynd.xlsx
+++ b/artfynd/A 60399-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123699075</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -872,6 +882,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134119897</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134635859</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1084,8 +1104,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134635860</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>